--- a/DummyJSON_QA_Test_Cases.xlsx
+++ b/DummyJSON_QA_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E-M-W-E\Desktop\Dummyjison-QA-Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA6A80D-D6BF-4794-9692-FCDDDF4F6CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B5839E-D889-422B-B2D4-052C6A66EA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Auth" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="733">
   <si>
     <t>Type</t>
   </si>
@@ -2239,6 +2239,9 @@
   </si>
   <si>
     <t>200 OK consistently; used as a pre-flight check before running the full suite</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Status</t>
   </si>
 </sst>
 </file>
@@ -2439,10 +2442,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2763,21 +2766,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2805,7 +2808,7 @@
         <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>732</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>23</v>
@@ -3415,21 +3418,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4067,21 +4070,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>656</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4653,21 +4656,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5503,21 +5506,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6122,21 +6125,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6576,21 +6579,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7030,21 +7033,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7517,21 +7520,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7938,21 +7941,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -8227,21 +8230,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
